--- a/case_studies/simplified_case/2025/technologies.xlsx
+++ b/case_studies/simplified_case/2025/technologies.xlsx
@@ -694,7 +694,7 @@
         <v>0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>78.39</v>
+        <v>0</v>
       </c>
       <c r="K2" s="3" t="n">
         <v>0</v>
@@ -703,10 +703,10 @@
         <v>0</v>
       </c>
       <c r="M2" s="3" t="n">
-        <v>946.41</v>
+        <v>0</v>
       </c>
       <c r="N2" s="3" t="n">
-        <v>946.41</v>
+        <v>0</v>
       </c>
       <c r="O2" s="3" t="n">
         <v>0</v>
@@ -724,7 +724,7 @@
         <v>0</v>
       </c>
       <c r="T2" s="3" t="n">
-        <v>159.94</v>
+        <v>0</v>
       </c>
       <c r="U2" s="3" t="n">
         <v>0</v>
@@ -773,7 +773,7 @@
         <v>0</v>
       </c>
       <c r="D3" s="5" t="n">
-        <v>45.66</v>
+        <v>0</v>
       </c>
       <c r="E3" s="5" t="n">
         <v>0</v>
@@ -782,19 +782,19 @@
         <v>0</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>8.08</v>
+        <v>0</v>
       </c>
       <c r="H3" s="5" t="n">
         <v>0</v>
       </c>
       <c r="I3" s="5" t="n">
-        <v>17.75</v>
+        <v>0</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>35.39</v>
+        <v>0</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>31.27</v>
+        <v>0</v>
       </c>
       <c r="L3" s="5" t="n">
         <v>0</v>
@@ -821,7 +821,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="5" t="n">
-        <v>17.75</v>
+        <v>0</v>
       </c>
       <c r="U3" s="5" t="n">
         <v>0</v>
@@ -839,7 +839,7 @@
         <v>0</v>
       </c>
       <c r="Z3" s="5" t="n">
-        <v>42.99</v>
+        <v>0</v>
       </c>
       <c r="AA3" s="5" t="n">
         <v>0</v>
@@ -870,7 +870,7 @@
         <v>0</v>
       </c>
       <c r="D4" s="3" t="n">
-        <v>39.95</v>
+        <v>0</v>
       </c>
       <c r="E4" s="3" t="n">
         <v>0</v>
@@ -879,34 +879,34 @@
         <v>0</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>7.07</v>
+        <v>0</v>
       </c>
       <c r="H4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>26.13</v>
+        <v>0</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>153.06</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>20.3</v>
+        <v>0</v>
       </c>
       <c r="L4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>1369.36</v>
+        <v>0</v>
       </c>
       <c r="N4" s="3" t="n">
-        <v>1369.36</v>
+        <v>0</v>
       </c>
       <c r="O4" s="3" t="n">
         <v>0</v>
       </c>
       <c r="P4" s="3" t="n">
-        <v>31.96</v>
+        <v>0</v>
       </c>
       <c r="Q4" s="3" t="n">
         <v>0</v>
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="T4" s="3" t="n">
-        <v>231.42</v>
+        <v>0</v>
       </c>
       <c r="U4" s="3" t="n">
         <v>0</v>
@@ -936,7 +936,7 @@
         <v>0</v>
       </c>
       <c r="Z4" s="3" t="n">
-        <v>27.91</v>
+        <v>0</v>
       </c>
       <c r="AA4" s="3" t="n">
         <v>0</v>
@@ -1064,7 +1064,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="3" t="n">
-        <v>62.79</v>
+        <v>0</v>
       </c>
       <c r="E6" s="3" t="n">
         <v>0</v>
@@ -1073,28 +1073,28 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>11.11</v>
+        <v>0</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>24.41</v>
+        <v>0</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>95.48999999999999</v>
+        <v>0</v>
       </c>
       <c r="K6" s="3" t="n">
-        <v>42.99</v>
+        <v>0</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>0</v>
       </c>
       <c r="M6" s="3" t="n">
-        <v>565.33</v>
+        <v>0</v>
       </c>
       <c r="N6" s="3" t="n">
-        <v>565.33</v>
+        <v>0</v>
       </c>
       <c r="O6" s="3" t="n">
         <v>0</v>
@@ -1112,7 +1112,7 @@
         <v>0</v>
       </c>
       <c r="T6" s="3" t="n">
-        <v>95.54000000000001</v>
+        <v>0</v>
       </c>
       <c r="U6" s="3" t="n">
         <v>0</v>
@@ -1130,7 +1130,7 @@
         <v>0</v>
       </c>
       <c r="Z6" s="3" t="n">
-        <v>59.12</v>
+        <v>0</v>
       </c>
       <c r="AA6" s="3" t="n">
         <v>0</v>
@@ -1176,10 +1176,10 @@
         <v>0</v>
       </c>
       <c r="I7" s="5" t="n">
-        <v>48.52</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>59.3</v>
+        <v>0</v>
       </c>
       <c r="K7" s="5" t="n">
         <v>0</v>
@@ -1197,7 +1197,7 @@
         <v>0</v>
       </c>
       <c r="P7" s="5" t="n">
-        <v>97.03</v>
+        <v>0</v>
       </c>
       <c r="Q7" s="5" t="n">
         <v>0</v>
@@ -1209,7 +1209,7 @@
         <v>0</v>
       </c>
       <c r="T7" s="5" t="n">
-        <v>48.52</v>
+        <v>0</v>
       </c>
       <c r="U7" s="5" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>0</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>54.11</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>0</v>
@@ -1285,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="M8" s="3" t="n">
-        <v>653.27</v>
+        <v>0</v>
       </c>
       <c r="N8" s="3" t="n">
-        <v>653.27</v>
+        <v>0</v>
       </c>
       <c r="O8" s="3" t="n">
         <v>0</v>
@@ -1306,7 +1306,7 @@
         <v>0</v>
       </c>
       <c r="T8" s="3" t="n">
-        <v>110.4</v>
+        <v>0</v>
       </c>
       <c r="U8" s="3" t="n">
         <v>0</v>
